--- a/data_processed/results_XGB_m2_floorarea_per_capitatenure.xlsx
+++ b/data_processed/results_XGB_m2_floorarea_per_capitatenure.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.8572" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.8526" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.026996612548828</v>
+        <v>4.979870319366455</v>
       </c>
       <c r="D2" t="n">
-        <v>19.5180606842041</v>
+        <v>21.9831600189209</v>
       </c>
     </row>
     <row r="3">
@@ -467,14 +467,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.506573677062988</v>
+        <v>3.53293776512146</v>
       </c>
       <c r="D3" t="n">
-        <v>29.14538764953613</v>
+        <v>15.5958137512207</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.403579235076904</v>
+        <v>7.679272174835205</v>
       </c>
       <c r="D4" t="n">
-        <v>9.332254409790039</v>
+        <v>33.89941024780273</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.183987140655518</v>
+        <v>2.328122854232788</v>
       </c>
       <c r="D5" t="n">
-        <v>16.24495315551758</v>
+        <v>10.27727508544922</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8590591549873352</v>
+        <v>2.705896139144897</v>
       </c>
       <c r="D6" t="n">
-        <v>3.335424900054932</v>
+        <v>11.94491863250732</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_middleschool</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.136571407318115</v>
+        <v>0.7247799634933472</v>
       </c>
       <c r="D7" t="n">
-        <v>8.29555606842041</v>
+        <v>3.199471712112427</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>distance_depstore</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3.638844966888428</v>
+        <v>0.7022353410720825</v>
       </c>
       <c r="D8" t="n">
-        <v>14.12835693359375</v>
+        <v>3.099950551986694</v>
       </c>
     </row>
   </sheetData>
